--- a/data/trans_bre/MCS12_SP_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/MCS12_SP_R2-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,52; 17,24</t>
+          <t>4,44; 16,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,64; 20,69</t>
+          <t>7,43; 20,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 16,75</t>
+          <t>4,17; 18,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 24,43</t>
+          <t>1,37; 22,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,36; 59,3</t>
+          <t>12,21; 57,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,35; 64,8</t>
+          <t>19,16; 63,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,24; 55,23</t>
+          <t>11,33; 62,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,01; 121,9</t>
+          <t>4,45; 110,84</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,92; 19,63</t>
+          <t>9,46; 20,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,84; 17,55</t>
+          <t>5,24; 17,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 9,17</t>
+          <t>-2,02; 9,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,98; 36,53</t>
+          <t>2,86; 34,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,47; 62,71</t>
+          <t>25,79; 64,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,23; 42,34</t>
+          <t>11,35; 43,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 21,08</t>
+          <t>-4,24; 21,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,26; 126,83</t>
+          <t>7,24; 114,37</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,66; 19,88</t>
+          <t>8,98; 20,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,35; 18,25</t>
+          <t>7,54; 18,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 7,15</t>
+          <t>-3,93; 7,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 13,11</t>
+          <t>2,48; 13,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,28; 49,17</t>
+          <t>18,95; 50,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,82; 37,96</t>
+          <t>14,05; 38,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 15,96</t>
+          <t>-7,68; 15,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,9; 39,84</t>
+          <t>6,28; 39,96</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,92; 23,8</t>
+          <t>11,33; 23,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 16,76</t>
+          <t>4,17; 16,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 13,14</t>
+          <t>1,92; 12,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,07; 37,82</t>
+          <t>3,09; 38,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,73; 57,11</t>
+          <t>23,95; 59,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,2; 33,36</t>
+          <t>7,06; 31,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 26,23</t>
+          <t>3,63; 25,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,57; 289,46</t>
+          <t>7,2; 313,56</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 9,8</t>
+          <t>-4,65; 10,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,03; 20,26</t>
+          <t>7,01; 20,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,96; 17,0</t>
+          <t>3,37; 17,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,84; 12,91</t>
+          <t>2,93; 13,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 19,2</t>
+          <t>-7,84; 19,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,09; 40,05</t>
+          <t>11,95; 38,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,57; 34,95</t>
+          <t>6,29; 36,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,55; 28,13</t>
+          <t>5,49; 28,49</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 10,49</t>
+          <t>-3,91; 10,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,98; 22,14</t>
+          <t>6,19; 22,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,68; 15,83</t>
+          <t>0,12; 15,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,1; 42,24</t>
+          <t>4,17; 41,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 20,56</t>
+          <t>-6,7; 21,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,78; 50,15</t>
+          <t>11,58; 48,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,29; 34,41</t>
+          <t>-0,01; 32,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,18; 98,25</t>
+          <t>8,36; 91,68</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 4,9</t>
+          <t>-12,83; 4,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 18,81</t>
+          <t>2,82; 19,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 14,35</t>
+          <t>-1,83; 13,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 13,99</t>
+          <t>2,45; 13,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 9,8</t>
+          <t>-21,54; 9,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,58; 37,09</t>
+          <t>4,54; 37,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 28,21</t>
+          <t>-2,93; 27,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,65; 27,25</t>
+          <t>4,19; 26,95</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,46; 13,38</t>
+          <t>8,51; 13,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,51; 15,29</t>
+          <t>10,49; 15,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,3; 9,38</t>
+          <t>4,39; 9,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,41; 24,88</t>
+          <t>9,23; 26,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,96; 32,03</t>
+          <t>19,18; 32,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,82; 32,26</t>
+          <t>20,81; 31,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,64; 20,07</t>
+          <t>8,93; 19,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>22,65; 74,33</t>
+          <t>22,49; 83,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/MCS12_SP_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/MCS12_SP_R2-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,35</t>
+          <t>7,95</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>27,14%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 16,77</t>
+          <t>4,33; 16,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,43; 20,7</t>
+          <t>6,89; 20,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,17; 18,17</t>
+          <t>3,44; 16,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 22,31</t>
+          <t>-1,39; 17,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,21; 57,84</t>
+          <t>11,53; 55,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,16; 63,87</t>
+          <t>17,6; 64,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,33; 62,18</t>
+          <t>9,4; 55,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 110,84</t>
+          <t>-4,2; 74,3</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,9</t>
+          <t>6,22</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,46; 20,24</t>
+          <t>8,6; 19,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,24; 17,24</t>
+          <t>5,42; 16,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 9,1</t>
+          <t>-2,46; 9,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 34,5</t>
+          <t>-1,1; 13,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,79; 64,18</t>
+          <t>22,85; 61,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,35; 43,21</t>
+          <t>11,7; 40,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 21,89</t>
+          <t>-4,89; 21,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,24; 114,37</t>
+          <t>-2,7; 47,5</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,92</t>
+          <t>9,28</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>25,68%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,98; 20,32</t>
+          <t>9,05; 20,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,54; 18,41</t>
+          <t>7,95; 18,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 7,15</t>
+          <t>-4,17; 6,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 13,21</t>
+          <t>3,35; 14,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,95; 50,16</t>
+          <t>19,31; 49,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,05; 38,84</t>
+          <t>14,96; 39,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 15,97</t>
+          <t>-8,12; 14,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,28; 39,96</t>
+          <t>8,32; 45,07</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,74</t>
+          <t>8,59</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>19,79%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,33; 23,86</t>
+          <t>11,52; 23,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,17; 16,05</t>
+          <t>3,7; 15,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 12,69</t>
+          <t>1,65; 13,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 38,9</t>
+          <t>3,9; 13,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,95; 59,23</t>
+          <t>23,25; 56,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,06; 31,68</t>
+          <t>6,51; 31,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,63; 25,21</t>
+          <t>3,05; 26,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,2; 313,56</t>
+          <t>8,22; 34,06</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,67</t>
+          <t>8,94</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 10,21</t>
+          <t>-3,79; 10,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,01; 20,03</t>
+          <t>6,79; 20,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,37; 17,28</t>
+          <t>3,49; 16,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,93; 13,14</t>
+          <t>4,24; 13,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 19,62</t>
+          <t>-6,49; 20,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,95; 38,38</t>
+          <t>11,14; 40,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,29; 36,16</t>
+          <t>6,13; 35,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,49; 28,49</t>
+          <t>8,09; 30,62</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21,15</t>
+          <t>7,34</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 10,81</t>
+          <t>-4,53; 10,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,19; 22,11</t>
+          <t>5,65; 21,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,12; 15,12</t>
+          <t>0,3; 15,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,17; 41,55</t>
+          <t>2,4; 13,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 21,67</t>
+          <t>-7,68; 20,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,58; 48,27</t>
+          <t>9,92; 45,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 32,06</t>
+          <t>1,04; 32,75</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,36; 91,68</t>
+          <t>4,56; 28,81</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,5</t>
+          <t>8,06</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 4,61</t>
+          <t>-12,79; 4,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 19,58</t>
+          <t>3,54; 19,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 13,81</t>
+          <t>-2,79; 13,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,45; 13,74</t>
+          <t>2,0; 13,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-21,54; 9,04</t>
+          <t>-21,29; 9,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,54; 37,38</t>
+          <t>5,65; 37,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 27,85</t>
+          <t>-4,75; 27,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,19; 26,95</t>
+          <t>3,95; 26,87</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15,17</t>
+          <t>8,92</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,51; 13,51</t>
+          <t>8,38; 13,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,49; 15,17</t>
+          <t>10,48; 15,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,39; 9,14</t>
+          <t>4,07; 8,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,23; 26,71</t>
+          <t>6,68; 10,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,18; 32,16</t>
+          <t>18,68; 32,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,81; 31,85</t>
+          <t>20,88; 32,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,93; 19,45</t>
+          <t>8,33; 19,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>22,49; 83,69</t>
+          <t>15,39; 27,09</t>
         </is>
       </c>
     </row>
